--- a/Files/USERS.xlsx
+++ b/Files/USERS.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_Files\Work\Projects\ThreatLens CS-232 (DBMS)\ThreatLens\Files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771802A0-33F7-40B8-A965-22315F579461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,112 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Usernames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passwords </t>
+  </si>
+  <si>
+    <t>-- GIKI University users (org_id=2)</t>
+  </si>
+  <si>
+    <t>ali.admin</t>
+  </si>
+  <si>
+    <t>sara.analyst</t>
+  </si>
+  <si>
+    <t>hassan.view</t>
+  </si>
+  <si>
+    <t>nadia.analyst</t>
+  </si>
+  <si>
+    <t>tariq.view</t>
+  </si>
+  <si>
+    <t>usman.admin</t>
+  </si>
+  <si>
+    <t>abdullahg.view</t>
+  </si>
+  <si>
+    <t>fatima.analyst</t>
+  </si>
+  <si>
+    <t>bilal.analyst</t>
+  </si>
+  <si>
+    <t>zara.view</t>
+  </si>
+  <si>
+    <t>ali0123</t>
+  </si>
+  <si>
+    <t>sara6415</t>
+  </si>
+  <si>
+    <t>hassaN36%^5</t>
+  </si>
+  <si>
+    <t>nadiafe5</t>
+  </si>
+  <si>
+    <t>tariq3#^5</t>
+  </si>
+  <si>
+    <t>Usman7495</t>
+  </si>
+  <si>
+    <t>FaTiMa7700</t>
+  </si>
+  <si>
+    <t>ABdullAh518</t>
+  </si>
+  <si>
+    <t>bilal3457</t>
+  </si>
+  <si>
+    <t>zara#$%^&amp;*(</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF8B949E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +152,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +443,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Files/USERS.xlsx
+++ b/Files/USERS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_Files\Work\Projects\ThreatLens CS-232 (DBMS)\ThreatLens\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Desktop\Semester_4\CS-232\DBMS Project\GitHub repo\ThreatLens\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771802A0-33F7-40B8-A965-22315F579461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F27F5F-A316-4C3A-A969-9A5577C8FD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="367" windowWidth="26300" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
   <si>
     <t>Usernames</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>zara#$%^&amp;*(</t>
+  </si>
+  <si>
+    <t>NEW Users</t>
   </si>
 </sst>
 </file>
@@ -444,14 +447,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.75" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -459,7 +462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -467,7 +470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -475,7 +478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -483,7 +486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -491,7 +494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -499,17 +502,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="5"/>
     </row>
-    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -517,7 +520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
@@ -525,7 +528,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -533,7 +536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -541,11 +544,114 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>22</v>
       </c>
     </row>

--- a/Files/USERS.xlsx
+++ b/Files/USERS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_Files\Work\Projects\ThreatLens CS-232 (DBMS)\ThreatLens\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771802A0-33F7-40B8-A965-22315F579461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E854B28E-35A0-4971-83A8-67FA2383D734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Files/USERS.xlsx
+++ b/Files/USERS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Desktop\Semester_4\CS-232\DBMS Project\GitHub repo\ThreatLens\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F27F5F-A316-4C3A-A969-9A5577C8FD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A979BB-6245-4E7E-835C-488C9CCECF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="367" windowWidth="26300" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-95" yWindow="0" windowWidth="13232" windowHeight="7064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
   <si>
     <t>Usernames</t>
   </si>
@@ -96,14 +96,86 @@
     <t>zara#$%^&amp;*(</t>
   </si>
   <si>
-    <t>NEW Users</t>
+    <t>ORG 1 (Allied Bank)</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>View</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>usman</t>
+  </si>
+  <si>
+    <t>fatima</t>
+  </si>
+  <si>
+    <t>abdullah</t>
+  </si>
+  <si>
+    <t>ali</t>
+  </si>
+  <si>
+    <t>sara</t>
+  </si>
+  <si>
+    <t>hassan</t>
+  </si>
+  <si>
+    <t>ORG 2 (Giki University)</t>
+  </si>
+  <si>
+    <t>ali_admin_who</t>
+  </si>
+  <si>
+    <t>analysing_sara</t>
+  </si>
+  <si>
+    <t>customer_101</t>
+  </si>
+  <si>
+    <t>ffa_123_xyz</t>
+  </si>
+  <si>
+    <t>Usman_Daffy</t>
+  </si>
+  <si>
+    <t>hacker_101^who</t>
+  </si>
+  <si>
+    <t>ORG 3 (Khyber Teaching Hospital)</t>
+  </si>
+  <si>
+    <t>dr.tariq</t>
+  </si>
+  <si>
+    <t>dr.asrar</t>
+  </si>
+  <si>
+    <t>dr.siraj</t>
+  </si>
+  <si>
+    <t>patients_123</t>
+  </si>
+  <si>
+    <t>chai_coffee_on_top</t>
+  </si>
+  <si>
+    <t>maths_nahi_rukni_chahiye</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +202,49 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -155,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -167,6 +282,19 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,11 +575,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.5" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
@@ -552,110 +680,151 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:3" ht="23.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="C19" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
+    <row r="26" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A31" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Files/USERS.xlsx
+++ b/Files/USERS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Desktop\Semester_4\CS-232\DBMS Project\GitHub repo\ThreatLens\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A979BB-6245-4E7E-835C-488C9CCECF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08C112B-B85F-455F-9BFF-7216A7B8C577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-95" yWindow="0" windowWidth="13232" windowHeight="7064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,75 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>Usernames</t>
   </si>
   <si>
     <t xml:space="preserve">Passwords </t>
-  </si>
-  <si>
-    <t>-- GIKI University users (org_id=2)</t>
-  </si>
-  <si>
-    <t>ali.admin</t>
-  </si>
-  <si>
-    <t>sara.analyst</t>
-  </si>
-  <si>
-    <t>hassan.view</t>
-  </si>
-  <si>
-    <t>nadia.analyst</t>
-  </si>
-  <si>
-    <t>tariq.view</t>
-  </si>
-  <si>
-    <t>usman.admin</t>
-  </si>
-  <si>
-    <t>abdullahg.view</t>
-  </si>
-  <si>
-    <t>fatima.analyst</t>
-  </si>
-  <si>
-    <t>bilal.analyst</t>
-  </si>
-  <si>
-    <t>zara.view</t>
-  </si>
-  <si>
-    <t>ali0123</t>
-  </si>
-  <si>
-    <t>sara6415</t>
-  </si>
-  <si>
-    <t>hassaN36%^5</t>
-  </si>
-  <si>
-    <t>nadiafe5</t>
-  </si>
-  <si>
-    <t>tariq3#^5</t>
-  </si>
-  <si>
-    <t>Usman7495</t>
-  </si>
-  <si>
-    <t>FaTiMa7700</t>
-  </si>
-  <si>
-    <t>ABdullAh518</t>
-  </si>
-  <si>
-    <t>bilal3457</t>
-  </si>
-  <si>
-    <t>zara#$%^&amp;*(</t>
   </si>
   <si>
     <t>ORG 1 (Allied Bank)</t>
@@ -175,7 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,20 +121,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF8B949E"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -270,31 +195,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,252 +495,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A2:C18"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.5" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="2" spans="1:3" ht="23.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="1" customFormat="1" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="23.8" x14ac:dyDescent="0.4">
-      <c r="A18" s="7" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B18" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-    </row>
-    <row r="25" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="5"/>
-    </row>
-    <row r="27" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-    </row>
-    <row r="31" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5"/>
-    </row>
-    <row r="32" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="21.1" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>25</v>
+      <c r="C18" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
